--- a/public/WEEK6_SHOPPING_LIST.xlsx
+++ b/public/WEEK6_SHOPPING_LIST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Vecka 6 Inköpslista" sheetId="1" r:id="rId1"/>
+    <sheet name="Vecka 6" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -619,13 +619,10 @@
         <v>Frukt/Grönt</v>
       </c>
       <c r="C15" t="str">
-        <v>ime</v>
+        <v>lime</v>
       </c>
       <c r="D15">
         <v>0.25</v>
-      </c>
-      <c r="E15" t="str">
-        <v>l</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +678,10 @@
         <v>Frukt/Grönt</v>
       </c>
       <c r="C19" t="str">
-        <v>ul lök</v>
+        <v>gul lök</v>
       </c>
       <c r="D19">
         <v>2</v>
-      </c>
-      <c r="E19" t="str">
-        <v>g</v>
       </c>
     </row>
     <row r="20">
@@ -1163,13 +1157,10 @@
         <v>Kryddor/smaksättare</v>
       </c>
       <c r="C50" t="str">
-        <v>färsk basilika</v>
+        <v>msk färsk basilika</v>
       </c>
       <c r="D50">
         <v>2</v>
-      </c>
-      <c r="E50" t="str">
-        <v>msk</v>
       </c>
     </row>
     <row r="51">
